--- a/AC_2009/AC_031.xlsx
+++ b/AC_2009/AC_031.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -515,6 +593,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -523,7 +602,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Candidate_1</t>
+          <t>PS_Name</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -18943,85 +19022,235 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B279" s="7">
-        <f>SUM(B6:B278)</f>
-        <v/>
-      </c>
-      <c r="C279" s="7">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr"/>
+      <c r="C279" s="9">
         <f>SUM(C6:C278)</f>
         <v/>
       </c>
-      <c r="D279" s="7">
+      <c r="D279" s="9">
         <f>SUM(D6:D278)</f>
         <v/>
       </c>
-      <c r="E279" s="7">
+      <c r="E279" s="9">
         <f>SUM(E6:E278)</f>
         <v/>
       </c>
-      <c r="F279" s="7">
+      <c r="F279" s="9">
         <f>SUM(F6:F278)</f>
         <v/>
       </c>
-      <c r="G279" s="7">
+      <c r="G279" s="9">
         <f>SUM(G6:G278)</f>
         <v/>
       </c>
-      <c r="H279" s="7">
+      <c r="H279" s="9">
         <f>SUM(H6:H278)</f>
         <v/>
       </c>
-      <c r="I279" s="7">
+      <c r="I279" s="9">
         <f>SUM(I6:I278)</f>
         <v/>
       </c>
-      <c r="J279" s="7">
+      <c r="J279" s="9">
         <f>SUM(J6:J278)</f>
         <v/>
       </c>
-      <c r="K279" s="7">
+      <c r="K279" s="9">
         <f>SUM(K6:K278)</f>
         <v/>
       </c>
-      <c r="L279" s="7">
+      <c r="L279" s="9">
         <f>SUM(L6:L278)</f>
         <v/>
       </c>
-      <c r="M279" s="7">
+      <c r="M279" s="9">
         <f>SUM(M6:M278)</f>
         <v/>
       </c>
-      <c r="N279" s="7">
+      <c r="N279" s="9">
         <f>SUM(N6:N278)</f>
         <v/>
       </c>
-      <c r="O279" s="7">
+      <c r="O279" s="9">
         <f>SUM(O6:O278)</f>
         <v/>
       </c>
-      <c r="P279" s="7">
+      <c r="P279" s="9">
         <f>SUM(P6:P278)</f>
         <v/>
       </c>
-      <c r="Q279" s="7">
+      <c r="Q279" s="9">
         <f>SUM(Q6:Q278)</f>
         <v/>
       </c>
-      <c r="R279" s="7">
+      <c r="R279" s="9">
         <f>SUM(R6:R278)</f>
         <v/>
       </c>
-      <c r="S279" s="7">
+      <c r="S279" s="9">
         <f>SUM(S6:S278)</f>
         <v/>
       </c>
-      <c r="T279" s="7">
+      <c r="T279" s="9">
         <f>SUM(T6:T278)</f>
+        <v/>
+      </c>
+      <c r="U279" s="9">
+        <f>SUM(U6:U278)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B280" s="11" t="inlineStr"/>
+      <c r="C280" s="11" t="n">
+        <v>318</v>
+      </c>
+      <c r="D280" s="11" t="n">
+        <v>251</v>
+      </c>
+      <c r="E280" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F280" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="J280" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="K280" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="11" t="n">
+        <v>642</v>
+      </c>
+      <c r="R280" s="11" t="n">
+        <v>234</v>
+      </c>
+      <c r="S280" s="11" t="n">
+        <v>876</v>
+      </c>
+      <c r="T280" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B281" s="13" t="inlineStr"/>
+      <c r="C281" s="13">
+        <f>C279+C280</f>
+        <v/>
+      </c>
+      <c r="D281" s="13">
+        <f>D279+D280</f>
+        <v/>
+      </c>
+      <c r="E281" s="13">
+        <f>E279+E280</f>
+        <v/>
+      </c>
+      <c r="F281" s="13">
+        <f>F279+F280</f>
+        <v/>
+      </c>
+      <c r="G281" s="13">
+        <f>G279+G280</f>
+        <v/>
+      </c>
+      <c r="H281" s="13">
+        <f>H279+H280</f>
+        <v/>
+      </c>
+      <c r="I281" s="13">
+        <f>I279+I280</f>
+        <v/>
+      </c>
+      <c r="J281" s="13">
+        <f>J279+J280</f>
+        <v/>
+      </c>
+      <c r="K281" s="13">
+        <f>K279+K280</f>
+        <v/>
+      </c>
+      <c r="L281" s="13">
+        <f>L279+L280</f>
+        <v/>
+      </c>
+      <c r="M281" s="13">
+        <f>M279+M280</f>
+        <v/>
+      </c>
+      <c r="N281" s="13">
+        <f>N279+N280</f>
+        <v/>
+      </c>
+      <c r="O281" s="13">
+        <f>O279+O280</f>
+        <v/>
+      </c>
+      <c r="P281" s="13">
+        <f>P279+P280</f>
+        <v/>
+      </c>
+      <c r="Q281" s="13">
+        <f>Q279+Q280</f>
+        <v/>
+      </c>
+      <c r="R281" s="13">
+        <f>R279+R280</f>
+        <v/>
+      </c>
+      <c r="S281" s="13">
+        <f>S279+S280</f>
+        <v/>
+      </c>
+      <c r="T281" s="13">
+        <f>T279+T280</f>
+        <v/>
+      </c>
+      <c r="U281" s="13">
+        <f>U279+U280</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_031.xlsx
+++ b/AC_2009/AC_031.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,6 +192,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -593,7 +627,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -19022,234 +19055,234 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="8" t="inlineStr">
+      <c r="A279" s="14" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B279" s="9" t="inlineStr"/>
-      <c r="C279" s="9">
+      <c r="B279" s="15" t="inlineStr"/>
+      <c r="C279" s="16">
         <f>SUM(C6:C278)</f>
         <v/>
       </c>
-      <c r="D279" s="9">
+      <c r="D279" s="16">
         <f>SUM(D6:D278)</f>
         <v/>
       </c>
-      <c r="E279" s="9">
+      <c r="E279" s="16">
         <f>SUM(E6:E278)</f>
         <v/>
       </c>
-      <c r="F279" s="9">
+      <c r="F279" s="16">
         <f>SUM(F6:F278)</f>
         <v/>
       </c>
-      <c r="G279" s="9">
+      <c r="G279" s="16">
         <f>SUM(G6:G278)</f>
         <v/>
       </c>
-      <c r="H279" s="9">
+      <c r="H279" s="16">
         <f>SUM(H6:H278)</f>
         <v/>
       </c>
-      <c r="I279" s="9">
+      <c r="I279" s="16">
         <f>SUM(I6:I278)</f>
         <v/>
       </c>
-      <c r="J279" s="9">
+      <c r="J279" s="16">
         <f>SUM(J6:J278)</f>
         <v/>
       </c>
-      <c r="K279" s="9">
+      <c r="K279" s="16">
         <f>SUM(K6:K278)</f>
         <v/>
       </c>
-      <c r="L279" s="9">
+      <c r="L279" s="16">
         <f>SUM(L6:L278)</f>
         <v/>
       </c>
-      <c r="M279" s="9">
+      <c r="M279" s="16">
         <f>SUM(M6:M278)</f>
         <v/>
       </c>
-      <c r="N279" s="9">
+      <c r="N279" s="16">
         <f>SUM(N6:N278)</f>
         <v/>
       </c>
-      <c r="O279" s="9">
+      <c r="O279" s="16">
         <f>SUM(O6:O278)</f>
         <v/>
       </c>
-      <c r="P279" s="9">
+      <c r="P279" s="16">
         <f>SUM(P6:P278)</f>
         <v/>
       </c>
-      <c r="Q279" s="9">
+      <c r="Q279" s="16">
         <f>SUM(Q6:Q278)</f>
         <v/>
       </c>
-      <c r="R279" s="9">
+      <c r="R279" s="16">
         <f>SUM(R6:R278)</f>
         <v/>
       </c>
-      <c r="S279" s="9">
+      <c r="S279" s="16">
         <f>SUM(S6:S278)</f>
         <v/>
       </c>
-      <c r="T279" s="9">
+      <c r="T279" s="16">
         <f>SUM(T6:T278)</f>
         <v/>
       </c>
-      <c r="U279" s="9">
+      <c r="U279" s="16">
         <f>SUM(U6:U278)</f>
         <v/>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="10" t="inlineStr">
+      <c r="A280" s="17" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr"/>
-      <c r="C280" s="11" t="n">
+      <c r="C280" s="16" t="n">
         <v>318</v>
       </c>
-      <c r="D280" s="11" t="n">
+      <c r="D280" s="16" t="n">
         <v>251</v>
       </c>
-      <c r="E280" s="11" t="n">
+      <c r="E280" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="F280" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G280" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I280" s="11" t="n">
+      <c r="F280" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="J280" s="11" t="n">
+      <c r="J280" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="K280" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L280" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q280" s="11" t="n">
+      <c r="K280" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="16" t="n">
         <v>642</v>
       </c>
-      <c r="R280" s="11" t="n">
+      <c r="R280" s="16" t="n">
         <v>234</v>
       </c>
-      <c r="S280" s="11" t="n">
+      <c r="S280" s="16" t="n">
         <v>876</v>
       </c>
-      <c r="T280" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U280" s="11" t="n">
+      <c r="T280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="12" t="inlineStr">
+      <c r="A281" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B281" s="13" t="inlineStr"/>
-      <c r="C281" s="13">
+      <c r="B281" s="19" t="inlineStr"/>
+      <c r="C281" s="20">
         <f>C279+C280</f>
         <v/>
       </c>
-      <c r="D281" s="13">
+      <c r="D281" s="20">
         <f>D279+D280</f>
         <v/>
       </c>
-      <c r="E281" s="13">
+      <c r="E281" s="20">
         <f>E279+E280</f>
         <v/>
       </c>
-      <c r="F281" s="13">
+      <c r="F281" s="20">
         <f>F279+F280</f>
         <v/>
       </c>
-      <c r="G281" s="13">
+      <c r="G281" s="20">
         <f>G279+G280</f>
         <v/>
       </c>
-      <c r="H281" s="13">
+      <c r="H281" s="20">
         <f>H279+H280</f>
         <v/>
       </c>
-      <c r="I281" s="13">
+      <c r="I281" s="20">
         <f>I279+I280</f>
         <v/>
       </c>
-      <c r="J281" s="13">
+      <c r="J281" s="20">
         <f>J279+J280</f>
         <v/>
       </c>
-      <c r="K281" s="13">
+      <c r="K281" s="20">
         <f>K279+K280</f>
         <v/>
       </c>
-      <c r="L281" s="13">
+      <c r="L281" s="20">
         <f>L279+L280</f>
         <v/>
       </c>
-      <c r="M281" s="13">
+      <c r="M281" s="20">
         <f>M279+M280</f>
         <v/>
       </c>
-      <c r="N281" s="13">
+      <c r="N281" s="20">
         <f>N279+N280</f>
         <v/>
       </c>
-      <c r="O281" s="13">
+      <c r="O281" s="20">
         <f>O279+O280</f>
         <v/>
       </c>
-      <c r="P281" s="13">
+      <c r="P281" s="20">
         <f>P279+P280</f>
         <v/>
       </c>
-      <c r="Q281" s="13">
+      <c r="Q281" s="20">
         <f>Q279+Q280</f>
         <v/>
       </c>
-      <c r="R281" s="13">
+      <c r="R281" s="20">
         <f>R279+R280</f>
         <v/>
       </c>
-      <c r="S281" s="13">
+      <c r="S281" s="20">
         <f>S279+S280</f>
         <v/>
       </c>
-      <c r="T281" s="13">
+      <c r="T281" s="20">
         <f>T279+T280</f>
         <v/>
       </c>
-      <c r="U281" s="13">
+      <c r="U281" s="20">
         <f>U279+U280</f>
         <v/>
       </c>

--- a/AC_2009/AC_031.xlsx
+++ b/AC_2009/AC_031.xlsx
@@ -1465,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U281"/>
+  <dimension ref="A1:T281"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" style="1" min="1" max="2"/>
@@ -1487,8 +1487,7 @@
     <col width="17" customWidth="1" style="1" min="18" max="18"/>
     <col width="16" customWidth="1" style="1" min="19" max="19"/>
     <col width="17" customWidth="1" style="1" min="20" max="20"/>
-    <col width="16" customWidth="1" style="1" min="21" max="21"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="22" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.35" customHeight="1" s="24">
@@ -1516,7 +1515,6 @@
       <c r="R1" s="3" t="n"/>
       <c r="S1" s="3" t="n"/>
       <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
     </row>
     <row r="2" ht="13.75" customHeight="1" s="24">
       <c r="A2" s="4" t="inlineStr">
@@ -1543,7 +1541,6 @@
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
-      <c r="U2" s="3" t="n"/>
     </row>
     <row r="3" ht="13.75" customHeight="1" s="24">
       <c r="A3" s="4" t="inlineStr">
@@ -1570,7 +1567,6 @@
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
     </row>
     <row r="4" ht="13.55" customHeight="1" s="24">
       <c r="A4" s="5" t="n"/>
@@ -1593,7 +1589,6 @@
       <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n"/>
       <c r="T4" s="5" t="n"/>
-      <c r="U4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.55" customHeight="1" s="24">
       <c r="A5" s="6" t="inlineStr">
@@ -1691,14 +1686,9 @@
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
         </is>
       </c>
     </row>
@@ -1765,9 +1755,6 @@
       <c r="T6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" ht="13.55" customHeight="1" s="24">
       <c r="A7" s="9" t="n">
@@ -1832,9 +1819,6 @@
       <c r="T7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U7" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="26.55" customHeight="1" s="24">
       <c r="A8" s="9" t="n">
@@ -1900,9 +1884,6 @@
       <c r="T8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" ht="13.55" customHeight="1" s="24">
       <c r="A9" s="9" t="n">
@@ -1967,9 +1948,6 @@
       <c r="T9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="24">
       <c r="A10" s="9" t="n">
@@ -2032,9 +2010,6 @@
         <v>409</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2101,9 +2076,6 @@
       <c r="T11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" ht="13.55" customHeight="1" s="24">
       <c r="A12" s="9" t="n">
@@ -2168,9 +2140,6 @@
       <c r="T12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="26.55" customHeight="1" s="24">
       <c r="A13" s="9" t="n">
@@ -2236,9 +2205,6 @@
       <c r="T13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="13.55" customHeight="1" s="24">
       <c r="A14" s="9" t="n">
@@ -2303,9 +2269,6 @@
       <c r="T14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U14" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" ht="13.55" customHeight="1" s="24">
       <c r="A15" s="9" t="n">
@@ -2370,9 +2333,6 @@
       <c r="T15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" ht="26.55" customHeight="1" s="24">
       <c r="A16" s="9" t="n">
@@ -2438,9 +2398,6 @@
       <c r="T16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" ht="13.55" customHeight="1" s="24">
       <c r="A17" s="9" t="n">
@@ -2505,9 +2462,6 @@
       <c r="T17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" ht="13.55" customHeight="1" s="24">
       <c r="A18" s="9" t="n">
@@ -2572,9 +2526,6 @@
       <c r="T18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" ht="13.55" customHeight="1" s="24">
       <c r="A19" s="9" t="n">
@@ -2639,9 +2590,6 @@
       <c r="T19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="13.55" customHeight="1" s="24">
       <c r="A20" s="9" t="n">
@@ -2706,9 +2654,6 @@
       <c r="T20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" ht="13.55" customHeight="1" s="24">
       <c r="A21" s="9" t="n">
@@ -2773,9 +2718,6 @@
       <c r="T21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" ht="13.55" customHeight="1" s="24">
       <c r="A22" s="9" t="n">
@@ -2840,9 +2782,6 @@
       <c r="T22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23" ht="13.55" customHeight="1" s="24">
       <c r="A23" s="9" t="n">
@@ -2907,9 +2846,6 @@
       <c r="T23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" ht="13.55" customHeight="1" s="24">
       <c r="A24" s="9" t="n">
@@ -2974,9 +2910,6 @@
       <c r="T24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="24">
       <c r="A25" s="9" t="n">
@@ -3041,9 +2974,6 @@
       <c r="T25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" ht="13.55" customHeight="1" s="24">
       <c r="A26" s="9" t="n">
@@ -3108,9 +3038,6 @@
       <c r="T26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="13.55" customHeight="1" s="24">
       <c r="A27" s="9" t="n">
@@ -3175,9 +3102,6 @@
       <c r="T27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" ht="26.55" customHeight="1" s="24">
       <c r="A28" s="9" t="n">
@@ -3243,9 +3167,6 @@
       <c r="T28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" ht="26.55" customHeight="1" s="24">
       <c r="A29" s="9" t="n">
@@ -3311,9 +3232,6 @@
       <c r="T29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U29" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" ht="26.55" customHeight="1" s="24">
       <c r="A30" s="9" t="n">
@@ -3379,9 +3297,6 @@
       <c r="T30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" ht="13.55" customHeight="1" s="24">
       <c r="A31" s="9" t="n">
@@ -3446,9 +3361,6 @@
       <c r="T31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32" ht="13.55" customHeight="1" s="24">
       <c r="A32" s="9" t="n">
@@ -3513,9 +3425,6 @@
       <c r="T32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" ht="13.55" customHeight="1" s="24">
       <c r="A33" s="9" t="n">
@@ -3580,9 +3489,6 @@
       <c r="T33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="13.55" customHeight="1" s="24">
       <c r="A34" s="9" t="n">
@@ -3647,9 +3553,6 @@
       <c r="T34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" ht="13.55" customHeight="1" s="24">
       <c r="A35" s="9" t="n">
@@ -3714,9 +3617,6 @@
       <c r="T35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" ht="13.55" customHeight="1" s="24">
       <c r="A36" s="9" t="n">
@@ -3781,9 +3681,6 @@
       <c r="T36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" ht="13.55" customHeight="1" s="24">
       <c r="A37" s="9" t="n">
@@ -3848,9 +3745,6 @@
       <c r="T37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" ht="13.55" customHeight="1" s="24">
       <c r="A38" s="9" t="n">
@@ -3915,9 +3809,6 @@
       <c r="T38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U38" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" ht="13.55" customHeight="1" s="24">
       <c r="A39" s="9" t="n">
@@ -3982,9 +3873,6 @@
       <c r="T39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" ht="13.55" customHeight="1" s="24">
       <c r="A40" s="9" t="n">
@@ -4049,9 +3937,6 @@
       <c r="T40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U40" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" ht="13.55" customHeight="1" s="24">
       <c r="A41" s="9" t="n">
@@ -4116,9 +4001,6 @@
       <c r="T41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U41" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42" ht="13.55" customHeight="1" s="24">
       <c r="A42" s="9" t="n">
@@ -4183,9 +4065,6 @@
       <c r="T42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U42" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" ht="13.55" customHeight="1" s="24">
       <c r="A43" s="9" t="n">
@@ -4250,9 +4129,6 @@
       <c r="T43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" ht="13.55" customHeight="1" s="24">
       <c r="A44" s="9" t="n">
@@ -4317,9 +4193,6 @@
       <c r="T44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" ht="13.55" customHeight="1" s="24">
       <c r="A45" s="9" t="n">
@@ -4384,9 +4257,6 @@
       <c r="T45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" ht="13.55" customHeight="1" s="24">
       <c r="A46" s="9" t="n">
@@ -4451,9 +4321,6 @@
       <c r="T46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47" ht="13.55" customHeight="1" s="24">
       <c r="A47" s="9" t="n">
@@ -4518,9 +4385,6 @@
       <c r="T47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="48" ht="13.55" customHeight="1" s="24">
       <c r="A48" s="9" t="n">
@@ -4585,9 +4449,6 @@
       <c r="T48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49" ht="13.55" customHeight="1" s="24">
       <c r="A49" s="9" t="n">
@@ -4652,9 +4513,6 @@
       <c r="T49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50" ht="13.55" customHeight="1" s="24">
       <c r="A50" s="9" t="n">
@@ -4719,9 +4577,6 @@
       <c r="T50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51" ht="13.55" customHeight="1" s="24">
       <c r="A51" s="9" t="n">
@@ -4786,9 +4641,6 @@
       <c r="T51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52" ht="13.55" customHeight="1" s="24">
       <c r="A52" s="9" t="n">
@@ -4853,9 +4705,6 @@
       <c r="T52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="53" ht="13.55" customHeight="1" s="24">
       <c r="A53" s="9" t="n">
@@ -4920,9 +4769,6 @@
       <c r="T53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="54" ht="13.55" customHeight="1" s="24">
       <c r="A54" s="9" t="n">
@@ -4987,9 +4833,6 @@
       <c r="T54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="55" ht="13.55" customHeight="1" s="24">
       <c r="A55" s="9" t="n">
@@ -5054,9 +4897,6 @@
       <c r="T55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56" ht="13.55" customHeight="1" s="24">
       <c r="A56" s="9" t="n">
@@ -5121,9 +4961,6 @@
       <c r="T56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57" ht="26.55" customHeight="1" s="24">
       <c r="A57" s="9" t="n">
@@ -5189,9 +5026,6 @@
       <c r="T57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58" ht="26.55" customHeight="1" s="24">
       <c r="A58" s="9" t="n">
@@ -5257,9 +5091,6 @@
       <c r="T58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59" ht="26.55" customHeight="1" s="24">
       <c r="A59" s="9" t="n">
@@ -5325,9 +5156,6 @@
       <c r="T59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60" ht="26.55" customHeight="1" s="24">
       <c r="A60" s="9" t="n">
@@ -5393,9 +5221,6 @@
       <c r="T60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61" ht="26.55" customHeight="1" s="24">
       <c r="A61" s="9" t="n">
@@ -5461,9 +5286,6 @@
       <c r="T61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U61" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62" ht="26.55" customHeight="1" s="24">
       <c r="A62" s="9" t="n">
@@ -5529,9 +5351,6 @@
       <c r="T62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63" ht="26.55" customHeight="1" s="24">
       <c r="A63" s="9" t="n">
@@ -5597,9 +5416,6 @@
       <c r="T63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64" ht="26.55" customHeight="1" s="24">
       <c r="A64" s="9" t="n">
@@ -5665,9 +5481,6 @@
       <c r="T64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65" ht="26.55" customHeight="1" s="24">
       <c r="A65" s="9" t="n">
@@ -5733,9 +5546,6 @@
       <c r="T65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" ht="26.55" customHeight="1" s="24">
       <c r="A66" s="9" t="n">
@@ -5801,9 +5611,6 @@
       <c r="T66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" ht="26.55" customHeight="1" s="24">
       <c r="A67" s="9" t="n">
@@ -5869,9 +5676,6 @@
       <c r="T67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" ht="26.55" customHeight="1" s="24">
       <c r="A68" s="9" t="n">
@@ -5937,9 +5741,6 @@
       <c r="T68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U68" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69" ht="26.55" customHeight="1" s="24">
       <c r="A69" s="9" t="n">
@@ -6005,9 +5806,6 @@
       <c r="T69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U69" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70" ht="13.55" customHeight="1" s="24">
       <c r="A70" s="9" t="n">
@@ -6072,9 +5870,6 @@
       <c r="T70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71" ht="13.55" customHeight="1" s="24">
       <c r="A71" s="9" t="n">
@@ -6139,9 +5934,6 @@
       <c r="T71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U71" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72" ht="13.55" customHeight="1" s="24">
       <c r="A72" s="9" t="n">
@@ -6206,9 +5998,6 @@
       <c r="T72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" ht="13.55" customHeight="1" s="24">
       <c r="A73" s="9" t="n">
@@ -6273,9 +6062,6 @@
       <c r="T73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" ht="13.55" customHeight="1" s="24">
       <c r="A74" s="9" t="n">
@@ -6340,9 +6126,6 @@
       <c r="T74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" ht="13.55" customHeight="1" s="24">
       <c r="A75" s="9" t="n">
@@ -6407,9 +6190,6 @@
       <c r="T75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U75" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" ht="13.55" customHeight="1" s="24">
       <c r="A76" s="9" t="n">
@@ -6474,9 +6254,6 @@
       <c r="T76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U76" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" ht="13.55" customHeight="1" s="24">
       <c r="A77" s="9" t="n">
@@ -6541,9 +6318,6 @@
       <c r="T77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78" ht="13.55" customHeight="1" s="24">
       <c r="A78" s="9" t="n">
@@ -6608,9 +6382,6 @@
       <c r="T78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" ht="13.55" customHeight="1" s="24">
       <c r="A79" s="9" t="n">
@@ -6675,9 +6446,6 @@
       <c r="T79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U79" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" ht="26.55" customHeight="1" s="24">
       <c r="A80" s="9" t="n">
@@ -6743,9 +6511,6 @@
       <c r="T80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U80" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81" ht="13.55" customHeight="1" s="24">
       <c r="A81" s="9" t="n">
@@ -6810,9 +6575,6 @@
       <c r="T81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U81" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82" ht="13.55" customHeight="1" s="24">
       <c r="A82" s="9" t="n">
@@ -6877,9 +6639,6 @@
       <c r="T82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83" ht="13.55" customHeight="1" s="24">
       <c r="A83" s="9" t="n">
@@ -6944,9 +6703,6 @@
       <c r="T83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U83" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84" ht="13.55" customHeight="1" s="24">
       <c r="A84" s="9" t="n">
@@ -7011,9 +6767,6 @@
       <c r="T84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" ht="13.55" customHeight="1" s="24">
       <c r="A85" s="9" t="n">
@@ -7078,9 +6831,6 @@
       <c r="T85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" ht="13.55" customHeight="1" s="24">
       <c r="A86" s="9" t="n">
@@ -7145,9 +6895,6 @@
       <c r="T86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87" ht="13.55" customHeight="1" s="24">
       <c r="A87" s="9" t="n">
@@ -7212,9 +6959,6 @@
       <c r="T87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U87" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88" ht="13.55" customHeight="1" s="24">
       <c r="A88" s="9" t="n">
@@ -7279,9 +7023,6 @@
       <c r="T88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U88" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89" ht="13.55" customHeight="1" s="24">
       <c r="A89" s="9" t="n">
@@ -7346,9 +7087,6 @@
       <c r="T89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="90" ht="26.55" customHeight="1" s="24">
       <c r="A90" s="9" t="n">
@@ -7414,9 +7152,6 @@
       <c r="T90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U90" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" ht="13.55" customHeight="1" s="24">
       <c r="A91" s="9" t="n">
@@ -7481,9 +7216,6 @@
       <c r="T91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U91" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92" ht="13.55" customHeight="1" s="24">
       <c r="A92" s="9" t="n">
@@ -7548,9 +7280,6 @@
       <c r="T92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="93" ht="13.55" customHeight="1" s="24">
       <c r="A93" s="9" t="n">
@@ -7615,9 +7344,6 @@
       <c r="T93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U93" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94" ht="13.55" customHeight="1" s="24">
       <c r="A94" s="9" t="n">
@@ -7682,9 +7408,6 @@
       <c r="T94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95" ht="13.55" customHeight="1" s="24">
       <c r="A95" s="9" t="n">
@@ -7749,9 +7472,6 @@
       <c r="T95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U95" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96" ht="13.55" customHeight="1" s="24">
       <c r="A96" s="9" t="n">
@@ -7816,9 +7536,6 @@
       <c r="T96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U96" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97" ht="13.55" customHeight="1" s="24">
       <c r="A97" s="9" t="n">
@@ -7883,9 +7600,6 @@
       <c r="T97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98" ht="13.55" customHeight="1" s="24">
       <c r="A98" s="9" t="n">
@@ -7950,9 +7664,6 @@
       <c r="T98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99" ht="13.55" customHeight="1" s="24">
       <c r="A99" s="9" t="n">
@@ -8017,9 +7728,6 @@
       <c r="T99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100" ht="13.55" customHeight="1" s="24">
       <c r="A100" s="9" t="n">
@@ -8084,9 +7792,6 @@
       <c r="T100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101" ht="13.55" customHeight="1" s="24">
       <c r="A101" s="9" t="n">
@@ -8151,9 +7856,6 @@
       <c r="T101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102" ht="13.55" customHeight="1" s="24">
       <c r="A102" s="9" t="n">
@@ -8218,9 +7920,6 @@
       <c r="T102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103" ht="13.55" customHeight="1" s="24">
       <c r="A103" s="9" t="n">
@@ -8285,9 +7984,6 @@
       <c r="T103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U103" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" ht="13.55" customHeight="1" s="24">
       <c r="A104" s="9" t="n">
@@ -8352,9 +8048,6 @@
       <c r="T104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105" ht="13.55" customHeight="1" s="24">
       <c r="A105" s="9" t="n">
@@ -8419,9 +8112,6 @@
       <c r="T105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="106" ht="26.55" customHeight="1" s="24">
       <c r="A106" s="9" t="n">
@@ -8487,9 +8177,6 @@
       <c r="T106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" ht="26.55" customHeight="1" s="24">
       <c r="A107" s="9" t="n">
@@ -8555,9 +8242,6 @@
       <c r="T107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="108" ht="13.55" customHeight="1" s="24">
       <c r="A108" s="9" t="n">
@@ -8622,9 +8306,6 @@
       <c r="T108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109" ht="13.55" customHeight="1" s="24">
       <c r="A109" s="9" t="n">
@@ -8689,9 +8370,6 @@
       <c r="T109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="110" ht="13.55" customHeight="1" s="24">
       <c r="A110" s="9" t="n">
@@ -8756,9 +8434,6 @@
       <c r="T110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U110" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="111" ht="13.55" customHeight="1" s="24">
       <c r="A111" s="9" t="n">
@@ -8823,9 +8498,6 @@
       <c r="T111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U111" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" ht="13.55" customHeight="1" s="24">
       <c r="A112" s="9" t="n">
@@ -8890,9 +8562,6 @@
       <c r="T112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113" ht="13.55" customHeight="1" s="24">
       <c r="A113" s="9" t="n">
@@ -8957,9 +8626,6 @@
       <c r="T113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U113" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114" ht="13.55" customHeight="1" s="24">
       <c r="A114" s="9" t="n">
@@ -9024,9 +8690,6 @@
       <c r="T114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U114" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" ht="13.55" customHeight="1" s="24">
       <c r="A115" s="9" t="n">
@@ -9091,9 +8754,6 @@
       <c r="T115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="116" ht="26.55" customHeight="1" s="24">
       <c r="A116" s="9" t="n">
@@ -9159,9 +8819,6 @@
       <c r="T116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="117" ht="13.55" customHeight="1" s="24">
       <c r="A117" s="9" t="n">
@@ -9226,9 +8883,6 @@
       <c r="T117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="118" ht="13.55" customHeight="1" s="24">
       <c r="A118" s="9" t="n">
@@ -9293,9 +8947,6 @@
       <c r="T118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119" ht="13.55" customHeight="1" s="24">
       <c r="A119" s="9" t="n">
@@ -9360,9 +9011,6 @@
       <c r="T119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120" ht="13.55" customHeight="1" s="24">
       <c r="A120" s="9" t="n">
@@ -9427,9 +9075,6 @@
       <c r="T120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="121" ht="13.55" customHeight="1" s="24">
       <c r="A121" s="9" t="n">
@@ -9494,9 +9139,6 @@
       <c r="T121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122" ht="13.55" customHeight="1" s="24">
       <c r="A122" s="9" t="n">
@@ -9561,9 +9203,6 @@
       <c r="T122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123" ht="13.55" customHeight="1" s="24">
       <c r="A123" s="9" t="n">
@@ -9628,9 +9267,6 @@
       <c r="T123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124" ht="13.55" customHeight="1" s="24">
       <c r="A124" s="9" t="n">
@@ -9695,9 +9331,6 @@
       <c r="T124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="125" ht="13.55" customHeight="1" s="24">
       <c r="A125" s="9" t="n">
@@ -9762,9 +9395,6 @@
       <c r="T125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="126" ht="13.55" customHeight="1" s="24">
       <c r="A126" s="9" t="n">
@@ -9829,9 +9459,6 @@
       <c r="T126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U126" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="127" ht="13.55" customHeight="1" s="24">
       <c r="A127" s="9" t="n">
@@ -9896,9 +9523,6 @@
       <c r="T127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U127" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128" ht="13.55" customHeight="1" s="24">
       <c r="A128" s="9" t="n">
@@ -9963,9 +9587,6 @@
       <c r="T128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129" ht="13.55" customHeight="1" s="24">
       <c r="A129" s="9" t="n">
@@ -10030,9 +9651,6 @@
       <c r="T129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="130" ht="13.55" customHeight="1" s="24">
       <c r="A130" s="9" t="n">
@@ -10097,9 +9715,6 @@
       <c r="T130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131" ht="13.55" customHeight="1" s="24">
       <c r="A131" s="9" t="n">
@@ -10164,9 +9779,6 @@
       <c r="T131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U131" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132" ht="13.55" customHeight="1" s="24">
       <c r="A132" s="9" t="n">
@@ -10231,9 +9843,6 @@
       <c r="T132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133" ht="26.55" customHeight="1" s="24">
       <c r="A133" s="9" t="n">
@@ -10299,9 +9908,6 @@
       <c r="T133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134" ht="13.55" customHeight="1" s="24">
       <c r="A134" s="9" t="n">
@@ -10366,9 +9972,6 @@
       <c r="T134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U134" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135" ht="13.55" customHeight="1" s="24">
       <c r="A135" s="9" t="n">
@@ -10433,9 +10036,6 @@
       <c r="T135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136" ht="13.55" customHeight="1" s="24">
       <c r="A136" s="9" t="n">
@@ -10500,9 +10100,6 @@
       <c r="T136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U136" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137" ht="13.55" customHeight="1" s="24">
       <c r="A137" s="9" t="n">
@@ -10567,9 +10164,6 @@
       <c r="T137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" ht="13.55" customHeight="1" s="24">
       <c r="A138" s="9" t="n">
@@ -10634,9 +10228,6 @@
       <c r="T138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U138" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" ht="13.55" customHeight="1" s="24">
       <c r="A139" s="9" t="n">
@@ -10701,9 +10292,6 @@
       <c r="T139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U139" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" ht="13.55" customHeight="1" s="24">
       <c r="A140" s="9" t="n">
@@ -10768,9 +10356,6 @@
       <c r="T140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U140" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="141" ht="13.55" customHeight="1" s="24">
       <c r="A141" s="9" t="n">
@@ -10835,9 +10420,6 @@
       <c r="T141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U141" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142" ht="13.55" customHeight="1" s="24">
       <c r="A142" s="9" t="n">
@@ -10902,9 +10484,6 @@
       <c r="T142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U142" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143" ht="13.55" customHeight="1" s="24">
       <c r="A143" s="9" t="n">
@@ -10969,9 +10548,6 @@
       <c r="T143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U143" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="144" ht="13.55" customHeight="1" s="24">
       <c r="A144" s="9" t="n">
@@ -11036,9 +10612,6 @@
       <c r="T144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="145" ht="13.55" customHeight="1" s="24">
       <c r="A145" s="9" t="n">
@@ -11103,9 +10676,6 @@
       <c r="T145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U145" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="146" ht="13.55" customHeight="1" s="24">
       <c r="A146" s="9" t="n">
@@ -11170,9 +10740,6 @@
       <c r="T146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U146" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="147" ht="13.55" customHeight="1" s="24">
       <c r="A147" s="9" t="n">
@@ -11237,9 +10804,6 @@
       <c r="T147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148" ht="13.55" customHeight="1" s="24">
       <c r="A148" s="9" t="n">
@@ -11304,9 +10868,6 @@
       <c r="T148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U148" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="149" ht="13.55" customHeight="1" s="24">
       <c r="A149" s="9" t="n">
@@ -11371,9 +10932,6 @@
       <c r="T149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U149" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="150" ht="13.55" customHeight="1" s="24">
       <c r="A150" s="9" t="n">
@@ -11438,9 +10996,6 @@
       <c r="T150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="151" ht="26.55" customHeight="1" s="24">
       <c r="A151" s="9" t="n">
@@ -11506,9 +11061,6 @@
       <c r="T151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="152" ht="13.55" customHeight="1" s="24">
       <c r="A152" s="9" t="n">
@@ -11573,9 +11125,6 @@
       <c r="T152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U152" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="153" ht="13.55" customHeight="1" s="24">
       <c r="A153" s="9" t="n">
@@ -11640,9 +11189,6 @@
       <c r="T153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U153" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="154" ht="13.55" customHeight="1" s="24">
       <c r="A154" s="9" t="n">
@@ -11707,9 +11253,6 @@
       <c r="T154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="155" ht="13.55" customHeight="1" s="24">
       <c r="A155" s="9" t="n">
@@ -11774,9 +11317,6 @@
       <c r="T155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U155" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="156" ht="13.55" customHeight="1" s="24">
       <c r="A156" s="9" t="n">
@@ -11841,9 +11381,6 @@
       <c r="T156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U156" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="157" ht="13.55" customHeight="1" s="24">
       <c r="A157" s="9" t="n">
@@ -11908,9 +11445,6 @@
       <c r="T157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U157" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="158" ht="26.55" customHeight="1" s="24">
       <c r="A158" s="9" t="n">
@@ -11976,9 +11510,6 @@
       <c r="T158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U158" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="159" ht="13.55" customHeight="1" s="24">
       <c r="A159" s="9" t="n">
@@ -12043,9 +11574,6 @@
       <c r="T159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U159" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="160" ht="13.55" customHeight="1" s="24">
       <c r="A160" s="9" t="n">
@@ -12110,9 +11638,6 @@
       <c r="T160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U160" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="161" ht="13.55" customHeight="1" s="24">
       <c r="A161" s="9" t="n">
@@ -12177,9 +11702,6 @@
       <c r="T161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U161" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="162" ht="13.55" customHeight="1" s="24">
       <c r="A162" s="9" t="n">
@@ -12244,9 +11766,6 @@
       <c r="T162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U162" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="163" ht="13.55" customHeight="1" s="24">
       <c r="A163" s="9" t="n">
@@ -12311,9 +11830,6 @@
       <c r="T163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U163" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="164" ht="13.55" customHeight="1" s="24">
       <c r="A164" s="9" t="n">
@@ -12378,9 +11894,6 @@
       <c r="T164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U164" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="165" ht="13.55" customHeight="1" s="24">
       <c r="A165" s="9" t="n">
@@ -12445,9 +11958,6 @@
       <c r="T165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U165" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="166" ht="13.55" customHeight="1" s="24">
       <c r="A166" s="9" t="n">
@@ -12512,9 +12022,6 @@
       <c r="T166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U166" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="167" ht="13.55" customHeight="1" s="24">
       <c r="A167" s="9" t="n">
@@ -12579,9 +12086,6 @@
       <c r="T167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U167" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="168" ht="13.55" customHeight="1" s="24">
       <c r="A168" s="9" t="n">
@@ -12646,9 +12150,6 @@
       <c r="T168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U168" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="169" ht="13.55" customHeight="1" s="24">
       <c r="A169" s="9" t="n">
@@ -12713,9 +12214,6 @@
       <c r="T169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U169" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="170" ht="13.55" customHeight="1" s="24">
       <c r="A170" s="9" t="n">
@@ -12780,9 +12278,6 @@
       <c r="T170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U170" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171" ht="13.55" customHeight="1" s="24">
       <c r="A171" s="9" t="n">
@@ -12847,9 +12342,6 @@
       <c r="T171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U171" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="172" ht="13.55" customHeight="1" s="24">
       <c r="A172" s="9" t="n">
@@ -12914,9 +12406,6 @@
       <c r="T172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U172" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173" ht="13.55" customHeight="1" s="24">
       <c r="A173" s="9" t="n">
@@ -12981,9 +12470,6 @@
       <c r="T173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U173" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="174" ht="13.55" customHeight="1" s="24">
       <c r="A174" s="9" t="n">
@@ -13048,9 +12534,6 @@
       <c r="T174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U174" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="175" ht="13.55" customHeight="1" s="24">
       <c r="A175" s="9" t="n">
@@ -13115,9 +12598,6 @@
       <c r="T175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U175" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="176" ht="13.55" customHeight="1" s="24">
       <c r="A176" s="9" t="n">
@@ -13182,9 +12662,6 @@
       <c r="T176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U176" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="177" ht="13.55" customHeight="1" s="24">
       <c r="A177" s="9" t="n">
@@ -13249,9 +12726,6 @@
       <c r="T177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U177" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="178" ht="13.55" customHeight="1" s="24">
       <c r="A178" s="9" t="n">
@@ -13316,9 +12790,6 @@
       <c r="T178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U178" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="179" ht="13.55" customHeight="1" s="24">
       <c r="A179" s="9" t="n">
@@ -13383,9 +12854,6 @@
       <c r="T179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U179" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="180" ht="13.55" customHeight="1" s="24">
       <c r="A180" s="9" t="n">
@@ -13450,9 +12918,6 @@
       <c r="T180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U180" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="181" ht="13.55" customHeight="1" s="24">
       <c r="A181" s="9" t="n">
@@ -13517,9 +12982,6 @@
       <c r="T181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U181" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="182" ht="13.55" customHeight="1" s="24">
       <c r="A182" s="9" t="n">
@@ -13584,9 +13046,6 @@
       <c r="T182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U182" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="183" ht="13.55" customHeight="1" s="24">
       <c r="A183" s="9" t="n">
@@ -13651,9 +13110,6 @@
       <c r="T183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U183" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="184" ht="13.55" customHeight="1" s="24">
       <c r="A184" s="9" t="n">
@@ -13718,9 +13174,6 @@
       <c r="T184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U184" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="185" ht="13.55" customHeight="1" s="24">
       <c r="A185" s="9" t="n">
@@ -13785,9 +13238,6 @@
       <c r="T185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U185" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="186" ht="13.55" customHeight="1" s="24">
       <c r="A186" s="9" t="n">
@@ -13852,9 +13302,6 @@
       <c r="T186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U186" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="187" ht="13.55" customHeight="1" s="24">
       <c r="A187" s="9" t="n">
@@ -13919,9 +13366,6 @@
       <c r="T187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U187" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="188" ht="13.55" customHeight="1" s="24">
       <c r="A188" s="9" t="n">
@@ -13986,9 +13430,6 @@
       <c r="T188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U188" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="189" ht="13.55" customHeight="1" s="24">
       <c r="A189" s="9" t="n">
@@ -14053,9 +13494,6 @@
       <c r="T189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U189" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="190" ht="13.55" customHeight="1" s="24">
       <c r="A190" s="9" t="n">
@@ -14120,9 +13558,6 @@
       <c r="T190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U190" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="191" ht="13.55" customHeight="1" s="24">
       <c r="A191" s="9" t="n">
@@ -14187,9 +13622,6 @@
       <c r="T191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U191" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="192" ht="26.55" customHeight="1" s="24">
       <c r="A192" s="9" t="n">
@@ -14255,9 +13687,6 @@
       <c r="T192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U192" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="193" ht="13.55" customHeight="1" s="24">
       <c r="A193" s="9" t="n">
@@ -14322,9 +13751,6 @@
       <c r="T193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U193" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="194" ht="13.55" customHeight="1" s="24">
       <c r="A194" s="9" t="n">
@@ -14389,9 +13815,6 @@
       <c r="T194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U194" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="195" ht="13.55" customHeight="1" s="24">
       <c r="A195" s="9" t="n">
@@ -14456,9 +13879,6 @@
       <c r="T195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U195" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="196" ht="13.55" customHeight="1" s="24">
       <c r="A196" s="9" t="n">
@@ -14523,9 +13943,6 @@
       <c r="T196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U196" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="197" ht="13.55" customHeight="1" s="24">
       <c r="A197" s="9" t="n">
@@ -14590,9 +14007,6 @@
       <c r="T197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U197" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="198" ht="13.55" customHeight="1" s="24">
       <c r="A198" s="9" t="n">
@@ -14657,9 +14071,6 @@
       <c r="T198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U198" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="199" ht="13.55" customHeight="1" s="24">
       <c r="A199" s="9" t="n">
@@ -14724,9 +14135,6 @@
       <c r="T199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U199" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="200" ht="13.55" customHeight="1" s="24">
       <c r="A200" s="9" t="n">
@@ -14791,9 +14199,6 @@
       <c r="T200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U200" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="201" ht="13.55" customHeight="1" s="24">
       <c r="A201" s="9" t="n">
@@ -14858,9 +14263,6 @@
       <c r="T201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U201" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="202" ht="13.55" customHeight="1" s="24">
       <c r="A202" s="9" t="n">
@@ -14925,9 +14327,6 @@
       <c r="T202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U202" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="203" ht="13.55" customHeight="1" s="24">
       <c r="A203" s="9" t="n">
@@ -14992,9 +14391,6 @@
       <c r="T203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U203" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="204" ht="13.55" customHeight="1" s="24">
       <c r="A204" s="9" t="n">
@@ -15059,9 +14455,6 @@
       <c r="T204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U204" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="205" ht="13.55" customHeight="1" s="24">
       <c r="A205" s="9" t="n">
@@ -15126,9 +14519,6 @@
       <c r="T205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U205" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="206" ht="26.55" customHeight="1" s="24">
       <c r="A206" s="9" t="n">
@@ -15194,9 +14584,6 @@
       <c r="T206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U206" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="207" ht="13.55" customHeight="1" s="24">
       <c r="A207" s="9" t="n">
@@ -15261,9 +14648,6 @@
       <c r="T207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U207" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="208" ht="13.55" customHeight="1" s="24">
       <c r="A208" s="9" t="n">
@@ -15328,9 +14712,6 @@
       <c r="T208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U208" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="209" ht="13.55" customHeight="1" s="24">
       <c r="A209" s="9" t="n">
@@ -15395,9 +14776,6 @@
       <c r="T209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U209" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="210" ht="13.55" customHeight="1" s="24">
       <c r="A210" s="9" t="n">
@@ -15462,9 +14840,6 @@
       <c r="T210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U210" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="211" ht="13.55" customHeight="1" s="24">
       <c r="A211" s="9" t="n">
@@ -15529,9 +14904,6 @@
       <c r="T211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U211" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="212" ht="13.55" customHeight="1" s="24">
       <c r="A212" s="9" t="n">
@@ -15596,9 +14968,6 @@
       <c r="T212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U212" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="213" ht="13.55" customHeight="1" s="24">
       <c r="A213" s="9" t="n">
@@ -15663,9 +15032,6 @@
       <c r="T213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U213" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="214" ht="13.55" customHeight="1" s="24">
       <c r="A214" s="9" t="n">
@@ -15730,9 +15096,6 @@
       <c r="T214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U214" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="215" ht="13.55" customHeight="1" s="24">
       <c r="A215" s="9" t="n">
@@ -15797,9 +15160,6 @@
       <c r="T215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U215" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="216" ht="13.55" customHeight="1" s="24">
       <c r="A216" s="9" t="n">
@@ -15864,9 +15224,6 @@
       <c r="T216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U216" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="217" ht="13.55" customHeight="1" s="24">
       <c r="A217" s="9" t="n">
@@ -15931,9 +15288,6 @@
       <c r="T217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U217" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="218" ht="13.55" customHeight="1" s="24">
       <c r="A218" s="9" t="n">
@@ -15998,9 +15352,6 @@
       <c r="T218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U218" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="219" ht="13.55" customHeight="1" s="24">
       <c r="A219" s="9" t="n">
@@ -16065,9 +15416,6 @@
       <c r="T219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U219" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="220" ht="13.55" customHeight="1" s="24">
       <c r="A220" s="9" t="n">
@@ -16132,9 +15480,6 @@
       <c r="T220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U220" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="221" ht="13.55" customHeight="1" s="24">
       <c r="A221" s="9" t="n">
@@ -16199,9 +15544,6 @@
       <c r="T221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U221" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="222" ht="13.55" customHeight="1" s="24">
       <c r="A222" s="9" t="n">
@@ -16266,9 +15608,6 @@
       <c r="T222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U222" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="223" ht="13.55" customHeight="1" s="24">
       <c r="A223" s="9" t="n">
@@ -16333,9 +15672,6 @@
       <c r="T223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U223" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="224" ht="13.55" customHeight="1" s="24">
       <c r="A224" s="9" t="n">
@@ -16400,9 +15736,6 @@
       <c r="T224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U224" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="225" ht="13.55" customHeight="1" s="24">
       <c r="A225" s="9" t="n">
@@ -16467,9 +15800,6 @@
       <c r="T225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U225" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="226" ht="13.55" customHeight="1" s="24">
       <c r="A226" s="9" t="n">
@@ -16534,9 +15864,6 @@
       <c r="T226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U226" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="227" ht="13.55" customHeight="1" s="24">
       <c r="A227" s="9" t="n">
@@ -16601,9 +15928,6 @@
       <c r="T227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U227" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="228" ht="13.55" customHeight="1" s="24">
       <c r="A228" s="9" t="n">
@@ -16668,9 +15992,6 @@
       <c r="T228" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U228" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="229" ht="13.55" customHeight="1" s="24">
       <c r="A229" s="9" t="n">
@@ -16735,9 +16056,6 @@
       <c r="T229" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U229" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="230" ht="13.55" customHeight="1" s="24">
       <c r="A230" s="9" t="n">
@@ -16802,9 +16120,6 @@
       <c r="T230" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U230" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="231" ht="13.55" customHeight="1" s="24">
       <c r="A231" s="9" t="n">
@@ -16869,9 +16184,6 @@
       <c r="T231" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U231" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="232" ht="13.55" customHeight="1" s="24">
       <c r="A232" s="9" t="n">
@@ -16936,9 +16248,6 @@
       <c r="T232" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U232" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="233" ht="13.55" customHeight="1" s="24">
       <c r="A233" s="9" t="n">
@@ -17003,9 +16312,6 @@
       <c r="T233" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U233" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="234" ht="13.55" customHeight="1" s="24">
       <c r="A234" s="9" t="n">
@@ -17070,9 +16376,6 @@
       <c r="T234" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U234" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="235" ht="13.55" customHeight="1" s="24">
       <c r="A235" s="9" t="n">
@@ -17137,9 +16440,6 @@
       <c r="T235" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U235" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="236" ht="13.55" customHeight="1" s="24">
       <c r="A236" s="9" t="n">
@@ -17204,9 +16504,6 @@
       <c r="T236" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U236" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="237" ht="13.55" customHeight="1" s="24">
       <c r="A237" s="9" t="n">
@@ -17271,9 +16568,6 @@
       <c r="T237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U237" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="238" ht="13.55" customHeight="1" s="24">
       <c r="A238" s="9" t="n">
@@ -17338,9 +16632,6 @@
       <c r="T238" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U238" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="239" ht="13.55" customHeight="1" s="24">
       <c r="A239" s="9" t="n">
@@ -17405,9 +16696,6 @@
       <c r="T239" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U239" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="240" ht="13.55" customHeight="1" s="24">
       <c r="A240" s="9" t="n">
@@ -17472,9 +16760,6 @@
       <c r="T240" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U240" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="241" ht="13.55" customHeight="1" s="24">
       <c r="A241" s="9" t="n">
@@ -17539,9 +16824,6 @@
       <c r="T241" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U241" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="242" ht="13.55" customHeight="1" s="24">
       <c r="A242" s="9" t="n">
@@ -17606,9 +16888,6 @@
       <c r="T242" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U242" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="243" ht="13.55" customHeight="1" s="24">
       <c r="A243" s="9" t="n">
@@ -17673,9 +16952,6 @@
       <c r="T243" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U243" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="244" ht="13.55" customHeight="1" s="24">
       <c r="A244" s="9" t="n">
@@ -17740,9 +17016,6 @@
       <c r="T244" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U244" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="245" ht="13.55" customHeight="1" s="24">
       <c r="A245" s="9" t="n">
@@ -17807,9 +17080,6 @@
       <c r="T245" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U245" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="246" ht="13.55" customHeight="1" s="24">
       <c r="A246" s="9" t="n">
@@ -17874,9 +17144,6 @@
       <c r="T246" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U246" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="247" ht="13.55" customHeight="1" s="24">
       <c r="A247" s="9" t="n">
@@ -17941,9 +17208,6 @@
       <c r="T247" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U247" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="248" ht="13.55" customHeight="1" s="24">
       <c r="A248" s="9" t="n">
@@ -18008,9 +17272,6 @@
       <c r="T248" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U248" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="249" ht="13.55" customHeight="1" s="24">
       <c r="A249" s="9" t="n">
@@ -18075,9 +17336,6 @@
       <c r="T249" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U249" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="250" ht="13.55" customHeight="1" s="24">
       <c r="A250" s="9" t="n">
@@ -18142,9 +17400,6 @@
       <c r="T250" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U250" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="251" ht="13.55" customHeight="1" s="24">
       <c r="A251" s="9" t="n">
@@ -18209,9 +17464,6 @@
       <c r="T251" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U251" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="252" ht="13.55" customHeight="1" s="24">
       <c r="A252" s="9" t="n">
@@ -18276,9 +17528,6 @@
       <c r="T252" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U252" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="253" ht="13.55" customHeight="1" s="24">
       <c r="A253" s="9" t="n">
@@ -18343,9 +17592,6 @@
       <c r="T253" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U253" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="254" ht="13.55" customHeight="1" s="24">
       <c r="A254" s="9" t="n">
@@ -18410,9 +17656,6 @@
       <c r="T254" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U254" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="255" ht="13.55" customHeight="1" s="24">
       <c r="A255" s="9" t="n">
@@ -18477,9 +17720,6 @@
       <c r="T255" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U255" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="256" ht="13.55" customHeight="1" s="24">
       <c r="A256" s="9" t="n">
@@ -18544,9 +17784,6 @@
       <c r="T256" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U256" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="257" ht="13.55" customHeight="1" s="24">
       <c r="A257" s="9" t="n">
@@ -18611,9 +17848,6 @@
       <c r="T257" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U257" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="258" ht="13.55" customHeight="1" s="24">
       <c r="A258" s="9" t="n">
@@ -18678,9 +17912,6 @@
       <c r="T258" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U258" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="259" ht="13.55" customHeight="1" s="24">
       <c r="A259" s="9" t="n">
@@ -18745,9 +17976,6 @@
       <c r="T259" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U259" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="260" ht="13.55" customHeight="1" s="24">
       <c r="A260" s="9" t="n">
@@ -18812,9 +18040,6 @@
       <c r="T260" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U260" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="261" ht="13.55" customHeight="1" s="24">
       <c r="A261" s="9" t="n">
@@ -18879,9 +18104,6 @@
       <c r="T261" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U261" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="262" ht="13.55" customHeight="1" s="24">
       <c r="A262" s="9" t="n">
@@ -18946,9 +18168,6 @@
       <c r="T262" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U262" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="263" ht="13.55" customHeight="1" s="24">
       <c r="A263" s="9" t="n">
@@ -19013,9 +18232,6 @@
       <c r="T263" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U263" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="264" ht="13.55" customHeight="1" s="24">
       <c r="A264" s="9" t="n">
@@ -19080,9 +18296,6 @@
       <c r="T264" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U264" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="265" ht="13.55" customHeight="1" s="24">
       <c r="A265" s="9" t="n">
@@ -19147,9 +18360,6 @@
       <c r="T265" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U265" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="266" ht="13.55" customHeight="1" s="24">
       <c r="A266" s="9" t="n">
@@ -19214,9 +18424,6 @@
       <c r="T266" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U266" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="267" ht="13.55" customHeight="1" s="24">
       <c r="A267" s="9" t="n">
@@ -19281,9 +18488,6 @@
       <c r="T267" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U267" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="268" ht="13.55" customHeight="1" s="24">
       <c r="A268" s="9" t="n">
@@ -19348,9 +18552,6 @@
       <c r="T268" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U268" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="269" ht="13.55" customHeight="1" s="24">
       <c r="A269" s="9" t="n">
@@ -19415,9 +18616,6 @@
       <c r="T269" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U269" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="270" ht="13.55" customHeight="1" s="24">
       <c r="A270" s="9" t="n">
@@ -19482,9 +18680,6 @@
       <c r="T270" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U270" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="271" ht="13.55" customHeight="1" s="24">
       <c r="A271" s="9" t="n">
@@ -19549,9 +18744,6 @@
       <c r="T271" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U271" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="272" ht="13.55" customHeight="1" s="24">
       <c r="A272" s="9" t="n">
@@ -19616,9 +18808,6 @@
       <c r="T272" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U272" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="273" ht="13.55" customHeight="1" s="24">
       <c r="A273" s="9" t="n">
@@ -19683,9 +18872,6 @@
       <c r="T273" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U273" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="274" ht="13.55" customHeight="1" s="24">
       <c r="A274" s="9" t="n">
@@ -19750,9 +18936,6 @@
       <c r="T274" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U274" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="275" ht="13.55" customHeight="1" s="24">
       <c r="A275" s="9" t="n">
@@ -19817,9 +19000,6 @@
       <c r="T275" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U275" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="276" ht="13.55" customHeight="1" s="24">
       <c r="A276" s="9" t="n">
@@ -19884,9 +19064,6 @@
       <c r="T276" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U276" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="277" ht="13.55" customHeight="1" s="24">
       <c r="A277" s="9" t="n">
@@ -19951,9 +19128,6 @@
       <c r="T277" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U277" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="278" ht="14.05" customHeight="1" s="24">
       <c r="A278" s="12" t="n">
@@ -20018,9 +19192,6 @@
       <c r="T278" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U278" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="279" ht="14.15" customHeight="1" s="24">
       <c r="A279" s="14" t="inlineStr">
@@ -20083,9 +19254,6 @@
       <c r="T279" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="U279" s="16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="280" ht="13.65" customHeight="1" s="24">
       <c r="A280" s="17" t="inlineStr">
@@ -20148,9 +19316,6 @@
       <c r="T280" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="U280" s="16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="281" ht="13.65" customHeight="1" s="24">
       <c r="A281" s="19" t="inlineStr">
@@ -20210,10 +19375,7 @@
       <c r="S281" s="22" t="n">
         <v>146412</v>
       </c>
-      <c r="T281" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U281" s="23" t="n">
+      <c r="T281" s="23" t="n">
         <v>0</v>
       </c>
     </row>
